--- a/astro-site/public/dl/paella-catering-business-plan/paella-catering-pricing-calculator.xlsx
+++ b/astro-site/public/dl/paella-catering-business-plan/paella-catering-pricing-calculator.xlsx
@@ -1260,19 +1260,19 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="32" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>20-lb propane cylinders to bring (plus one spare)</t>
+          <t>20-lb propane cylinders to bring (one per burner, plus one spare)</t>
         </is>
       </c>
       <c r="B50" s="12">
-        <f>ROUNDUP($B$49/20,0)+1</f>
-        <v>2.0</v>
+        <f>MAX($B$46,ROUNDUP($B$49/20,0))+1</f>
+        <v>3.0</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Never run a pan on a nearly empty cylinder.</t>
+          <t>One cylinder per burner that runs at the same time: a 20-lb cylinder cannot feed several 3-ring burners at full flame. Never start a pan on a nearly empty cylinder.</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="47" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Suggested servers and attendants for this package</t>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>From the package table below.</t>
+          <t>Paella chefs and helper as suggested above, plus about one server per 25 guests on top of them for a buffet with attendants. Miami Grill Catering's rule of thumb, one team member per 25 guests in total, is the lean end (miamigrillcatering.com).</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Cooked at the commissary in the paella pans and delivered hot in insulated carriers, no servers on site. Keep it at 135 °F (57 °C) or above, or label the time it left hot holding and discard it 4 hours later (time as a public health control, only if your county accepts it).</t>
+          <t>Cooked at the commissary, portioned into foil or hotel pans and delivered hot in insulated carriers, no servers on site. Keep it at 135 °F (57 °C) or above, or label the time it left hot holding and discard it 4 hours later (time as a public health control, only if your county accepts it).</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Paella chef, helper and servers for weddings and corporate events: about one team member per 25 guests (miamigrillcatering.com).</t>
+          <t>Paella chefs and a helper as suggested, plus about one server per 25 guests for weddings and corporate events with a staffed buffet (Kit estimate; miamigrillcatering.com counts about one team member per 25 guests in total, the lean end).</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Kit estimate: 1.2 quarts per lb (2.5 liters per kg); bomba rice absorbs up to 3 times its volume. The uncooked rice per guest comes from the "Pricing Calculator" tab.</t>
+          <t>Kit estimate: 1.2 quarts per lb (2.5 liters per kg) for most paella rice; bomba absorbs more, so plan up to 1.45 quarts per lb (3 liters per kg), a little more when you cook outdoors in the wind. The uncooked rice per guest comes from the "Pricing Calculator" tab.</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Needs an XL 3-ring burner and wind guards; check that your burner fits it.</t>
+          <t>Needs a burner rated for 40 in (100 cm) pans, larger than the XL 3-ring for pans up to 36 in, plus wind guards.</t>
         </is>
       </c>
     </row>
@@ -3846,32 +3846,32 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>20-lb propane cylinders (plus one spare)</t>
+          <t>20-lb propane cylinders (one per burner, plus one spare)</t>
         </is>
       </c>
       <c r="B36" s="12">
-        <f>ROUNDUP(B$35/20,0)+1</f>
+        <f>MAX(B$16,ROUNDUP(B$35/20,0))+1</f>
+        <v>3.0</v>
+      </c>
+      <c r="C36" s="12">
+        <f>MAX(C$16,ROUNDUP(C$35/20,0))+1</f>
         <v>2.0</v>
       </c>
-      <c r="C36" s="12">
-        <f>ROUNDUP(C$35/20,0)+1</f>
-        <v>2.0</v>
-      </c>
       <c r="D36" s="12">
-        <f>ROUNDUP(D$35/20,0)+1</f>
-        <v>2.0</v>
+        <f>MAX(D$16,ROUNDUP(D$35/20,0))+1</f>
+        <v>3.0</v>
       </c>
       <c r="E36" s="12">
-        <f>ROUNDUP(E$35/20,0)+1</f>
-        <v>2.0</v>
+        <f>MAX(E$16,ROUNDUP(E$35/20,0))+1</f>
+        <v>5.0</v>
       </c>
       <c r="F36" s="12">
-        <f>ROUNDUP(F$35/20,0)+1</f>
-        <v>3.0</v>
+        <f>MAX(F$16,ROUNDUP(F$35/20,0))+1</f>
+        <v>9.0</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>They travel upright and secured in the van.</t>
+          <t>One per burner that runs at the same time, plus a spare. They travel upright and secured in the van.</t>
         </is>
       </c>
     </row>
@@ -4928,20 +4928,20 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>20-lb propane cylinders to bring (plus one spare)</t>
+          <t>20-lb propane cylinders to bring (one per burner, plus one spare)</t>
         </is>
       </c>
       <c r="B50" s="12">
-        <f>ROUNDUP($B$49/20,0)+1</f>
+        <f>MAX($B$46,ROUNDUP($B$49/20,0))+1</f>
         <v>2.0</v>
       </c>
       <c r="C50" s="12">
-        <f>ROUNDUP($C$49/20,0)+1</f>
-        <v>2.0</v>
+        <f>MAX($C$46,ROUNDUP($C$49/20,0))+1</f>
+        <v>3.0</v>
       </c>
       <c r="D50" s="12">
-        <f>ROUNDUP($D$49/20,0)+1</f>
-        <v>2.0</v>
+        <f>MAX($D$46,ROUNDUP($D$49/20,0))+1</f>
+        <v>4.0</v>
       </c>
     </row>
     <row r="51">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Chicken &amp; seafood paella for an office, cooked at the commissary and delivered hot in its pan (20-guest minimum). It lands within 10% of the $22 drop-off line of the example mix in the Word plan (section 3).</t>
+          <t>Chicken &amp; seafood paella for an office, cooked at the commissary, portioned into foil or hotel pans and delivered hot in insulated carriers (20-guest minimum). It lands within 10% of the $22 drop-off line of the example mix in the Word plan (section 3).</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Wedding with a tapas hour, two paella chefs, a helper and five servers, dishes and flatware rented and passed through, and a 10% service charge; 50-guest minimum. The price per guest lands within 10% of the $52 wedding line of the example mix in the Word plan, inside the $44-65 of a full Spanish menu with staff (miamigrillcatering.com, zola.com).</t>
+          <t>Wedding with a tapas hour, two paella chefs (one runs the tapas hour while the other starts the pans), a helper and five servers, dishes and flatware rented (your cost, with your margin on top) and a 10% service charge; 50-guest minimum. The price per guest lands within 10% of the $52 wedding line of the example mix in the Word plan, inside the $44-65 of a full Spanish menu with staff (miamigrillcatering.com, zola.com).</t>
         </is>
       </c>
     </row>
